--- a/mysql/数据库增长量计算.xlsx
+++ b/mysql/数据库增长量计算.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9765"/>
+    <workbookView windowWidth="24000" windowHeight="9495"/>
   </bookViews>
   <sheets>
     <sheet name="修改每秒新值" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -98,11 +98,70 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -114,6 +173,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -123,14 +213,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -138,90 +221,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,14 +237,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,19 +251,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,120 +335,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -396,42 +432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,24 +442,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -474,6 +456,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,17 +499,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,10 +548,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,133 +560,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="6">
-        <v>144.97</v>
+        <v>50.52</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B4" s="8">
         <f>IF(C4="KB",B2/60*B3*1024,IF(C4="MB",B2/60*B3,IF(C4="GB",B2/60*B3/1024,IF(C4="TB",B2/60*B3/1024/1024))))</f>
-        <v>865.954133333333</v>
+        <v>301.7728</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>12</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B5" s="8">
         <f>IF(C5="KB",(B2/60)*1440*B3*1024,IF(C5="MB",(B2/60)*1440*B3,IF(C5="GB",(B2/60)*1440*B3/1024,IF(C5="TB",(B2/60)*1440*B3/1024/1024))))</f>
-        <v>1.18920703125</v>
+        <v>0.414421875</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>15</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B6" s="8">
         <f>IF(C6="KB",(B2/60)*1440*30*B3*1024,IF(C6="MB",(B2/60)*1440*30*B3,IF(C6="GB",(B2/60)*1440*30*B3/1024,IF(C6="TB",(B2/60)*1440*30*B3/1024/1024))))</f>
-        <v>35.6762109375</v>
+        <v>12.43265625</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>15</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B7" s="8">
         <f>IF(C7="KB",(B2/60)*1440*30*3*B3*1024,IF(C7="MB",(B2/60)*1440*30*3*B3,IF(C7="GB",(B2/60)*1440*30*3*B3/1024,IF(C7="TB",(B2/60)*1440*30*3*B3/1024/1024))))</f>
-        <v>107.0286328125</v>
+        <v>37.29796875</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>15</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B8" s="8">
         <f>IF(C8="KB",(B2/60)*1440*30*3*4*B3*1024,IF(C8="MB",(B2/60)*1440*30*3*4*B3,IF(C8="GB",(B2/60)*1440*30*3*4*B3/1024,IF(C8="TB",(B2/60)*1440*30*3*4*B3/1024/1024))))</f>
-        <v>428.11453125</v>
+        <v>149.191875</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>15</v>
